--- a/sample-data/Admin_contracts_2026-05-05.xlsx
+++ b/sample-data/Admin_contracts_2026-05-05.xlsx
@@ -430,19 +430,19 @@
         <v>CON-01</v>
       </c>
       <c r="B2" t="str">
-        <v>Vertex Insurance Pvt Ltd</v>
+        <v>Summit Insurance Pvt Ltd</v>
       </c>
       <c r="C2" t="str">
-        <v>Insurance</v>
+        <v>Other</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-05-22</v>
+        <v>2024-12-23</v>
       </c>
       <c r="E2" t="str">
         <v>2026-04-20</v>
       </c>
       <c r="F2">
-        <v>1274779</v>
+        <v>855946</v>
       </c>
       <c r="G2" t="str">
         <v>Auto</v>
@@ -456,19 +456,19 @@
         <v>CON-02</v>
       </c>
       <c r="B3" t="str">
-        <v>Acme Insurance Pvt Ltd</v>
+        <v>Zenith Tech Pvt Ltd</v>
       </c>
       <c r="C3" t="str">
         <v>Insurance</v>
       </c>
       <c r="D3" t="str">
-        <v>2024-05-19</v>
+        <v>2025-07-02</v>
       </c>
       <c r="E3" t="str">
         <v>2026-03-15</v>
       </c>
       <c r="F3">
-        <v>924114</v>
+        <v>799890</v>
       </c>
       <c r="G3" t="str">
         <v>Pending</v>
@@ -482,22 +482,22 @@
         <v>CON-03</v>
       </c>
       <c r="B4" t="str">
-        <v>Zenith Tech Pvt Ltd</v>
+        <v>Zenith Facilities Pvt Ltd</v>
       </c>
       <c r="C4" t="str">
         <v>Other</v>
       </c>
       <c r="D4" t="str">
-        <v>2024-05-17</v>
+        <v>2023-12-15</v>
       </c>
       <c r="E4" t="str">
         <v>2026-05-20</v>
       </c>
       <c r="F4">
-        <v>1270626</v>
+        <v>575145</v>
       </c>
       <c r="G4" t="str">
-        <v>Pending</v>
+        <v>Auto</v>
       </c>
       <c r="H4" t="str">
         <v>Admin Team</v>
@@ -508,22 +508,22 @@
         <v>CON-04</v>
       </c>
       <c r="B5" t="str">
-        <v>Vertex Tech Pvt Ltd</v>
+        <v>Vertex Facilities Pvt Ltd</v>
       </c>
       <c r="C5" t="str">
         <v>Insurance</v>
       </c>
       <c r="D5" t="str">
-        <v>2023-05-27</v>
+        <v>2025-05-19</v>
       </c>
       <c r="E5" t="str">
         <v>2026-05-28</v>
       </c>
       <c r="F5">
-        <v>526413</v>
+        <v>501106</v>
       </c>
       <c r="G5" t="str">
-        <v>Pending</v>
+        <v>Auto</v>
       </c>
       <c r="H5" t="str">
         <v>Admin Team</v>
@@ -534,22 +534,22 @@
         <v>CON-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Zenith Tech Pvt Ltd</v>
+        <v>Summit Tech Pvt Ltd</v>
       </c>
       <c r="C6" t="str">
-        <v>Insurance</v>
+        <v>Facilities</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-12-12</v>
+        <v>2024-12-28</v>
       </c>
       <c r="E6" t="str">
         <v>2026-06-10</v>
       </c>
       <c r="F6">
-        <v>1352906</v>
+        <v>480011</v>
       </c>
       <c r="G6" t="str">
-        <v>Auto</v>
+        <v>Pending</v>
       </c>
       <c r="H6" t="str">
         <v>Admin Team</v>
@@ -560,19 +560,19 @@
         <v>CON-06</v>
       </c>
       <c r="B7" t="str">
-        <v>Summit Facilities Pvt Ltd</v>
+        <v>Acme Facilities Pvt Ltd</v>
       </c>
       <c r="C7" t="str">
-        <v>Facilities</v>
+        <v>Other</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-07-08</v>
+        <v>2025-04-11</v>
       </c>
       <c r="E7" t="str">
         <v>2026-06-25</v>
       </c>
       <c r="F7">
-        <v>1224406</v>
+        <v>1473142</v>
       </c>
       <c r="G7" t="str">
         <v>Auto</v>
@@ -586,19 +586,19 @@
         <v>CON-07</v>
       </c>
       <c r="B8" t="str">
-        <v>Summit Facilities Pvt Ltd</v>
+        <v>Acme Facilities Pvt Ltd</v>
       </c>
       <c r="C8" t="str">
-        <v>License</v>
+        <v>Insurance</v>
       </c>
       <c r="D8" t="str">
-        <v>2023-09-22</v>
+        <v>2025-02-15</v>
       </c>
       <c r="E8" t="str">
         <v>2026-07-15</v>
       </c>
       <c r="F8">
-        <v>590664</v>
+        <v>611322</v>
       </c>
       <c r="G8" t="str">
         <v>Pending</v>
@@ -612,22 +612,22 @@
         <v>CON-08</v>
       </c>
       <c r="B9" t="str">
-        <v>Vertex Services Pvt Ltd</v>
+        <v>Vertex Tech Pvt Ltd</v>
       </c>
       <c r="C9" t="str">
-        <v>License</v>
+        <v>Other</v>
       </c>
       <c r="D9" t="str">
-        <v>2024-04-27</v>
+        <v>2025-05-27</v>
       </c>
       <c r="E9" t="str">
         <v>2026-08-01</v>
       </c>
       <c r="F9">
-        <v>1335498</v>
+        <v>383897</v>
       </c>
       <c r="G9" t="str">
-        <v>In-progress</v>
+        <v>Auto</v>
       </c>
       <c r="H9" t="str">
         <v>Admin Team</v>
@@ -638,22 +638,22 @@
         <v>CON-09</v>
       </c>
       <c r="B10" t="str">
-        <v>Pinnacle Services Pvt Ltd</v>
+        <v>Vertex Services Pvt Ltd</v>
       </c>
       <c r="C10" t="str">
         <v>Facilities</v>
       </c>
       <c r="D10" t="str">
-        <v>2023-02-23</v>
+        <v>2023-03-05</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-09-04</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F10">
-        <v>327150</v>
+        <v>312316</v>
       </c>
       <c r="G10" t="str">
-        <v>Pending</v>
+        <v>Auto</v>
       </c>
       <c r="H10" t="str">
         <v>Admin Team</v>
@@ -664,19 +664,19 @@
         <v>CON-10</v>
       </c>
       <c r="B11" t="str">
-        <v>Vertex Insurance Pvt Ltd</v>
+        <v>Zenith Insurance Pvt Ltd</v>
       </c>
       <c r="C11" t="str">
-        <v>Other</v>
+        <v>IT</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-07-21</v>
+        <v>2025-02-25</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-11-27</v>
+        <v>2026-10-12</v>
       </c>
       <c r="F11">
-        <v>959353</v>
+        <v>624623</v>
       </c>
       <c r="G11" t="str">
         <v>Pending</v>
@@ -690,19 +690,19 @@
         <v>CON-11</v>
       </c>
       <c r="B12" t="str">
-        <v>Pinnacle Insurance Pvt Ltd</v>
+        <v>Pinnacle Facilities Pvt Ltd</v>
       </c>
       <c r="C12" t="str">
-        <v>Insurance</v>
+        <v>Other</v>
       </c>
       <c r="D12" t="str">
-        <v>2024-03-15</v>
+        <v>2024-02-13</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-10-09</v>
+        <v>2026-09-01</v>
       </c>
       <c r="F12">
-        <v>667122</v>
+        <v>674793</v>
       </c>
       <c r="G12" t="str">
         <v>In-progress</v>
@@ -716,22 +716,22 @@
         <v>CON-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Zenith Insurance Pvt Ltd</v>
+        <v>Pinnacle Tech Pvt Ltd</v>
       </c>
       <c r="C13" t="str">
         <v>Other</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-11-12</v>
+        <v>2024-10-24</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-11-23</v>
+        <v>2026-10-21</v>
       </c>
       <c r="F13">
-        <v>403456</v>
+        <v>314678</v>
       </c>
       <c r="G13" t="str">
-        <v>In-progress</v>
+        <v>Auto</v>
       </c>
       <c r="H13" t="str">
         <v>Admin Team</v>
@@ -742,22 +742,22 @@
         <v>CON-13</v>
       </c>
       <c r="B14" t="str">
-        <v>Pinnacle Services Pvt Ltd</v>
+        <v>Pinnacle Tech Pvt Ltd</v>
       </c>
       <c r="C14" t="str">
         <v>License</v>
       </c>
       <c r="D14" t="str">
-        <v>2023-08-25</v>
+        <v>2024-07-12</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-09-07</v>
+        <v>2026-11-15</v>
       </c>
       <c r="F14">
-        <v>334886</v>
+        <v>530138</v>
       </c>
       <c r="G14" t="str">
-        <v>Auto</v>
+        <v>Pending</v>
       </c>
       <c r="H14" t="str">
         <v>Admin Team</v>
@@ -768,22 +768,22 @@
         <v>CON-14</v>
       </c>
       <c r="B15" t="str">
-        <v>Summit Insurance Pvt Ltd</v>
+        <v>Vertex Services Pvt Ltd</v>
       </c>
       <c r="C15" t="str">
-        <v>License</v>
+        <v>Other</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-02-23</v>
+        <v>2025-06-13</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="F15">
-        <v>1056200</v>
+        <v>501110</v>
       </c>
       <c r="G15" t="str">
-        <v>Pending</v>
+        <v>In-progress</v>
       </c>
       <c r="H15" t="str">
         <v>Admin Team</v>
@@ -794,19 +794,19 @@
         <v>CON-15</v>
       </c>
       <c r="B16" t="str">
-        <v>Vertex Tech Pvt Ltd</v>
+        <v>Summit Tech Pvt Ltd</v>
       </c>
       <c r="C16" t="str">
-        <v>IT</v>
+        <v>Insurance</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-12-21</v>
+        <v>2024-10-28</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-11-10</v>
+        <v>2026-12-08</v>
       </c>
       <c r="F16">
-        <v>677528</v>
+        <v>712915</v>
       </c>
       <c r="G16" t="str">
         <v>Pending</v>
@@ -820,22 +820,22 @@
         <v>CON-16</v>
       </c>
       <c r="B17" t="str">
-        <v>Acme Insurance Pvt Ltd</v>
+        <v>Zenith Facilities Pvt Ltd</v>
       </c>
       <c r="C17" t="str">
-        <v>License</v>
+        <v>Other</v>
       </c>
       <c r="D17" t="str">
-        <v>2024-01-16</v>
+        <v>2024-04-23</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-26</v>
       </c>
       <c r="F17">
-        <v>1325586</v>
+        <v>270208</v>
       </c>
       <c r="G17" t="str">
-        <v>Auto</v>
+        <v>Pending</v>
       </c>
       <c r="H17" t="str">
         <v>Admin Team</v>
